--- a/Unit_Test_Plan_v0.1 (1).xlsx
+++ b/Unit_Test_Plan_v0.1 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI-Agent-Coordination-Engine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671CBF37-118B-4645-88A5-349581663EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EAB6F5-A07D-4EDC-B9C0-740AE00F905C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="78">
   <si>
     <t>Actual Result</t>
   </si>
@@ -142,12 +142,156 @@
   <si>
     <t>Sl.No:</t>
   </si>
+  <si>
+    <t>Expense Policy Tool Integration</t>
+  </si>
+  <si>
+    <t>Invoke the Expense Policy Tool with the expense type "travel" and observe the returned policy details.</t>
+  </si>
+  <si>
+    <t>A valid expense category with a corresponding policy is provided.</t>
+  </si>
+  <si>
+    <t>The tool should retrieve the applicable expense category, reimbursement limit, receipt requirement, and approval condition.</t>
+  </si>
+  <si>
+    <t>The tool successfully returned the Domestic Travel policy with a ₹3,500 reimbursement limit, mandatory receipt requirement, and approval condition.</t>
+  </si>
+  <si>
+    <t>Above-Limit Expense Analysis</t>
+  </si>
+  <si>
+    <t>Submit a travel expense of ₹10,000 through the CLI and observe the agent's policy-based analysis.</t>
+  </si>
+  <si>
+    <t>The claimed expense exceeds the simulated travel reimbursement limit of ₹3,500.</t>
+  </si>
+  <si>
+    <t>The agent should identify the excess amount, mention the applicable policy condition, and recommend further review.</t>
+  </si>
+  <si>
+    <t>The agent identified the ₹6,500 excess over the travel limit and recommended manager/finance review.</t>
+  </si>
+  <si>
+    <t>Receipt Validation with Complete Details</t>
+  </si>
+  <si>
+    <t>Enter an expense with receipt available, merchant name, receipt date, and receipt amount. Submit it through the CLI.</t>
+  </si>
+  <si>
+    <t>Receipt availability is confirmed and all required receipt fields are provided.</t>
+  </si>
+  <si>
+    <t>The Receipt Validation Tool should return a successful basic completeness check, and the agent should consider the validation and policy results in its audit.</t>
+  </si>
+  <si>
+    <t>Receipt validation and policy retrieval succeeded, and the agent generated an audit. Receipt validation was invoked twice in the initial run; duplicate registration was subsequently removed.</t>
+  </si>
+  <si>
+    <t>Receipt Unavailability Handling</t>
+  </si>
+  <si>
+    <t>Submit a travel expense through the CLI and select "no" when asked whether a receipt is available.</t>
+  </si>
+  <si>
+    <t>The employee does not have a receipt for the submitted expense.</t>
+  </si>
+  <si>
+    <t>The tool should identify the missing receipt, and the agent should flag the documentation concern and recommend manual review.</t>
+  </si>
+  <si>
+    <t>The tool returned "Receipt is not available. Manual review required." The agent identified the missing receipt and recommended further review.</t>
+  </si>
+  <si>
+    <t>Incomplete Receipt Details Handling</t>
+  </si>
+  <si>
+    <t>Submit an expense with receipt available but leave the merchant name blank.</t>
+  </si>
+  <si>
+    <t>A required receipt field is missing while other receipt details are provided.</t>
+  </si>
+  <si>
+    <t>The tool should identify the missing merchant information and return an incomplete receipt message.</t>
+  </si>
+  <si>
+    <t>The tool identified the missing merchant, and the agent reflected the incomplete receipt details in its audit.</t>
+  </si>
+  <si>
+    <t>Invalid Receipt Amount Handling</t>
+  </si>
+  <si>
+    <t>Submit an expense with receipt available and enter ₹0 as the receipt amount.</t>
+  </si>
+  <si>
+    <t>The receipt amount is zero and therefore invalid for the completeness check.</t>
+  </si>
+  <si>
+    <t>The tool should flag the invalid amount. The system should handle any subsequent AI service failure without treating the audit as successfully completed.</t>
+  </si>
+  <si>
+    <t>The tool correctly flagged the invalid receipt amount. However, the AI audit did not complete, and the test requires a successful rerun or error diagnosis.</t>
+  </si>
+  <si>
+    <t>Unknown Expense Category Handling</t>
+  </si>
+  <si>
+    <t>Submit an expense using an unsupported category such as "internet".</t>
+  </si>
+  <si>
+    <t>No matching company policy exists for the provided expense category.</t>
+  </si>
+  <si>
+    <t>The agent should state that no matching policy was found and that compliance cannot be confirmed.</t>
+  </si>
+  <si>
+    <t>Receipt and Claim Amount Mismatch</t>
+  </si>
+  <si>
+    <t>Submit an expense with a claim amount of ₹3,000 and a receipt amount of ₹2,500.</t>
+  </si>
+  <si>
+    <t>The receipt amount differs from the claimed expense amount.</t>
+  </si>
+  <si>
+    <t>The agent should identify the discrepancy and recommend further review.</t>
+  </si>
+  <si>
+    <t>Expense and Receipt Date Mismatch</t>
+  </si>
+  <si>
+    <t>Submit an expense with an expense date different from the receipt date.</t>
+  </si>
+  <si>
+    <t>The expense date and receipt date do not match.</t>
+  </si>
+  <si>
+    <t>The agent should preserve both dates and flag the discrepancy for review where relevant.</t>
+  </si>
+  <si>
+    <t>Gemini API Failure Handling</t>
+  </si>
+  <si>
+    <t>Test the agent when the Gemini API request fails, and observe the system's response.</t>
+  </si>
+  <si>
+    <t>Gemini is unavailable or returns an API error during expense analysis.</t>
+  </si>
+  <si>
+    <t>The system should display a clear error message and avoid presenting an incomplete audit as a successful result.</t>
+  </si>
+  <si>
+    <t>The receipt validation tool detected the mismatch between the claimed amount (₹3,000) and receipt amount (₹2,500). It returned “REQUIRES REVIEW” and recommended further review.</t>
+  </si>
+  <si>
+    <t>The receipt validation tool detected the date discrepancy between the expense date (2026-09-13) and receipt date (2026-08-13). It returned “REQUIRES REVIEW” and flagged the discrepancy.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -171,6 +315,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri "/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri "/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -186,7 +338,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -209,22 +361,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -541,15 +716,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" customWidth="1"/>
-    <col min="2" max="2" width="27.08984375" customWidth="1"/>
-    <col min="3" max="3" width="30.6328125" customWidth="1"/>
-    <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="31.36328125" customWidth="1"/>
-    <col min="6" max="6" width="27.08984375" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.08984375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="30.6328125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="33" style="5" customWidth="1"/>
+    <col min="5" max="5" width="31.36328125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="27.08984375" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.5">
@@ -571,108 +747,321 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" ht="64.5" customHeight="1">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7" ht="70.5" customHeight="1">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7" ht="62.5">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:7" ht="139.5">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" ht="75">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="2"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" ht="62.5">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" ht="50">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" ht="87.5">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:7" ht="62.5">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:7" ht="50">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:7" ht="75">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="1:7" ht="37.5">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="1:7" ht="97.5" customHeight="1">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:7" ht="100.5" customHeight="1">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:7" ht="50">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:1" ht="15.5">
+      <c r="A17" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unit_Test_Plan_v0.1 (1).xlsx
+++ b/Unit_Test_Plan_v0.1 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI-Agent-Coordination-Engine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EAB6F5-A07D-4EDC-B9C0-740AE00F905C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3954CE-77C7-4A4F-9531-CAD03D354460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="80">
   <si>
     <t>Actual Result</t>
   </si>
@@ -105,26 +105,6 @@
     <t>The system should collect the details, send them to the Expense Audit Agent and display the generated audit result.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Provide employee expense details to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>analyze_expense()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
     <t>Policy Information Handling</t>
   </si>
   <si>
@@ -230,9 +210,6 @@
     <t>The tool should flag the invalid amount. The system should handle any subsequent AI service failure without treating the audit as successfully completed.</t>
   </si>
   <si>
-    <t>The tool correctly flagged the invalid receipt amount. However, the AI audit did not complete, and the test requires a successful rerun or error diagnosis.</t>
-  </si>
-  <si>
     <t>Unknown Expense Category Handling</t>
   </si>
   <si>
@@ -242,9 +219,6 @@
     <t>No matching company policy exists for the provided expense category.</t>
   </si>
   <si>
-    <t>The agent should state that no matching policy was found and that compliance cannot be confirmed.</t>
-  </si>
-  <si>
     <t>Receipt and Claim Amount Mismatch</t>
   </si>
   <si>
@@ -278,13 +252,28 @@
     <t>Gemini is unavailable or returns an API error during expense analysis.</t>
   </si>
   <si>
-    <t>The system should display a clear error message and avoid presenting an incomplete audit as a successful result.</t>
-  </si>
-  <si>
     <t>The receipt validation tool detected the mismatch between the claimed amount (₹3,000) and receipt amount (₹2,500). It returned “REQUIRES REVIEW” and recommended further review.</t>
   </si>
   <si>
     <t>The receipt validation tool detected the date discrepancy between the expense date (2026-09-13) and receipt date (2026-08-13). It returned “REQUIRES REVIEW” and flagged the discrepancy.</t>
+  </si>
+  <si>
+    <t>Provide employee expense details to analyze_expense().</t>
+  </si>
+  <si>
+    <t>The receipt validation tool correctly flagged the invalid receipt amount. However, the AI audit did not complete due to a subsequent service/API failure. A successful end-to-end rerun is pending.</t>
+  </si>
+  <si>
+    <t>The agent should indicate that no matching company policy was found for the provided expense category. Compliance should remain unconfirmed, and the agent should recommend clarification or manual review without assuming policy limits.</t>
+  </si>
+  <si>
+    <t>Not tested yet. The actual system response must be recorded after submitting an expense with an unsupported category.</t>
+  </si>
+  <si>
+    <t>The system should display a clear AI service error or unavailable message and must not present an incomplete audit as a successfully completed result.</t>
+  </si>
+  <si>
+    <t>The Gemini exception-handling test confirmed that an AI service failure returns an explicit unavailable response. End-to-end error display through the web interface remains to be verified.</t>
   </si>
 </sst>
 </file>
@@ -296,18 +285,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial Unicode MS"/>
     </font>
     <font>
       <sz val="12"/>
@@ -321,6 +298,18 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Calibri "/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="Calibri "/>
     </font>
   </fonts>
@@ -376,30 +365,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -719,35 +711,35 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.08984375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="30.6328125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="33" style="5" customWidth="1"/>
-    <col min="5" max="5" width="31.36328125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="27.08984375" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="5"/>
+    <col min="1" max="1" width="9.1796875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="27.08984375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="30.6328125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="33" style="7" customWidth="1"/>
+    <col min="5" max="5" width="31.36328125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="27.08984375" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.5">
-      <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="15.5">
+      <c r="A1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="6"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7" ht="64.5" customHeight="1">
       <c r="A2" s="2">
@@ -768,7 +760,7 @@
       <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="G2" s="8"/>
     </row>
     <row r="3" spans="1:7" ht="70.5" customHeight="1">
       <c r="A3" s="2">
@@ -799,7 +791,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>16</v>
@@ -812,26 +804,26 @@
       </c>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:7" ht="139.5">
+    <row r="5" spans="1:7" ht="170.5">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="3"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" ht="75">
       <c r="A6" s="2">
@@ -850,28 +842,28 @@
         <v>22</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" ht="62.5">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="G7" s="6"/>
     </row>
@@ -880,19 +872,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="G8" s="6"/>
     </row>
@@ -901,19 +893,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="G9" s="6"/>
     </row>
@@ -922,19 +914,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="G10" s="6"/>
     </row>
@@ -943,125 +935,129 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="G11" s="6"/>
     </row>
-    <row r="12" spans="1:7" ht="75">
+    <row r="12" spans="1:7" ht="87.5">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="F12" s="3" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G12" s="6"/>
     </row>
-    <row r="13" spans="1:7" ht="37.5">
+    <row r="13" spans="1:7" ht="87.5">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="1:7" ht="97.5" customHeight="1">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="6"/>
-    </row>
-    <row r="14" spans="1:7" ht="97.5" customHeight="1">
-      <c r="A14" s="7">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="s">
+      <c r="E14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="F14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:7" ht="100.5" customHeight="1">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="C15" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="D15" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:7" ht="100.5" customHeight="1">
-      <c r="A15" s="7">
-        <v>14</v>
-      </c>
-      <c r="B15" s="8" t="s">
+      <c r="E15" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>77</v>
+      <c r="F15" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="G15" s="6"/>
     </row>
-    <row r="16" spans="1:7" ht="50">
+    <row r="16" spans="1:7" ht="87.5">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="3"/>
+        <v>78</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:1" ht="15.5">
-      <c r="A17" s="4"/>
+      <c r="A17" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unit_Test_Plan_v0.1 (1).xlsx
+++ b/Unit_Test_Plan_v0.1 (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI-Agent-Coordination-Engine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3954CE-77C7-4A4F-9531-CAD03D354460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F432BD5-180E-49AB-B253-27DB0425B5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="145">
   <si>
     <t>Actual Result</t>
   </si>
@@ -274,6 +274,201 @@
   </si>
   <si>
     <t>The Gemini exception-handling test confirmed that an AI service failure returns an explicit unavailable response. End-to-end error display through the web interface remains to be verified.</t>
+  </si>
+  <si>
+    <t>Multi-Agent Workflow Execution (End-to-End Coordination)</t>
+  </si>
+  <si>
+    <t>Invoke CoordinatorAgent.run_audit() with valid expense and receipt details (Employee: John Doe, Amount: ₹1000, Domestic Travel, valid receipt).</t>
+  </si>
+  <si>
+    <t>Complete multi-agent pipeline: Coordinator -&gt; Policy Agent -&gt; Receipt Agent -&gt; Analysis Agent -&gt; Decision Support Agent.</t>
+  </si>
+  <si>
+    <t>Workflow statuses for Policy, Receipt, Analysis, and Decision Support agents should all return 'Completed', and a final synthesized audit report should be generated.</t>
+  </si>
+  <si>
+    <t>Pass – Verified via automated unit test test_normal_expense_workflow (mocked LLM). All 4 agent statuses returned 'Completed' and final report was generated.</t>
+  </si>
+  <si>
+    <t>Policy Agent JSON Knowledge Base Retrieval</t>
+  </si>
+  <si>
+    <t>Execute Policy Agent analysis for category 'Domestic Travel' using get_expense_policy tool.</t>
+  </si>
+  <si>
+    <t>Policy Agent binds policy lookup tool and reads policy rule from local JSON knowledge base (knowledge/expense_policies.json).</t>
+  </si>
+  <si>
+    <t>Policy tool successfully retrieves Domestic Travel reimbursement limit (₹3,500) and approval conditions from JSON knowledge file.</t>
+  </si>
+  <si>
+    <t>Pass – Verified via automated unit test test_successful_policy_retrieval (mocked LLM tool-call binding). Policy limit of ₹3,500 retrieved.</t>
+  </si>
+  <si>
+    <t>Over-Limit Expense Multi-Agent Evaluation</t>
+  </si>
+  <si>
+    <t>Submit an expense exceeding category policy limit (e.g. ₹10,000 for Business Meals where limit is ₹1,500).</t>
+  </si>
+  <si>
+    <t>Policy Agent detects over-limit amount and passes findings downstream through Analysis and Decision Support agents.</t>
+  </si>
+  <si>
+    <t>Policy and Receipt agents complete successfully; Analysis Agent highlights excess amount, and Decision Support Agent recommends managerial review.</t>
+  </si>
+  <si>
+    <t>Pass – Verified via automated unit test test_over_limit_expense (mocked LLM). All workflow stages completed and excess amount flagged.</t>
+  </si>
+  <si>
+    <t>Missing Receipt Multi-Agent Audit</t>
+  </si>
+  <si>
+    <t>Submit an expense with receipt_available = False to CoordinatorAgent.run_audit().</t>
+  </si>
+  <si>
+    <t>Receipt Agent detects missing receipt and invokes validate_receipt tool returning manual review requirement.</t>
+  </si>
+  <si>
+    <t>Receipt Agent returns 'Completed' with findings indicating receipt not available and manual review required. Downstream agents integrate missing documentation note.</t>
+  </si>
+  <si>
+    <t>Pass – Verified via automated unit test test_missing_receipt (mocked LLM). Workflow completed with missing receipt flagged.</t>
+  </si>
+  <si>
+    <t>Receipt Amount and Date Discrepancy Checks</t>
+  </si>
+  <si>
+    <t>Submit expense claim of ₹2,000 with a receipt showing ₹1,000.</t>
+  </si>
+  <si>
+    <t>Receipt Agent invokes validate_receipt tool to detect mismatch between claimed and receipt amounts.</t>
+  </si>
+  <si>
+    <t>Receipt validation tool returns 'REQUIRES REVIEW' with explicit amount mismatch note; Analysis Agent incorporates discrepancy.</t>
+  </si>
+  <si>
+    <t>Pass – Verified via automated unit test test_receipt_amount_mismatch (mocked LLM). Amount mismatch detected and flagged as REQUIRES REVIEW.</t>
+  </si>
+  <si>
+    <t>Specialized Agent Failure Isolation</t>
+  </si>
+  <si>
+    <t>Simulate an exception during Policy Agent execution (e.g. API Error) during coordinator workflow execution.</t>
+  </si>
+  <si>
+    <t>Coordinator Agent catches specialized agent failure, marks workflow status for policy as 'Failed', and passes error message downstream without crashing overall pipeline.</t>
+  </si>
+  <si>
+    <t>Policy Agent status recorded as 'Failed', while remaining agents complete and system returns transparent failure status.</t>
+  </si>
+  <si>
+    <t>Pass – Verified via automated unit test test_agent_failure (mocked exception). Policy status set to 'Failed', remaining workflow completed gracefully.</t>
+  </si>
+  <si>
+    <t>Receipt Validation Tool Failure Handling</t>
+  </si>
+  <si>
+    <t>Simulate an exception inside validate_receipt.invoke() (e.g. unexpected database connection timeout).</t>
+  </si>
+  <si>
+    <t>Receipt Agent catches tool exception and returns formatted error string without crashing Coordinator pipeline.</t>
+  </si>
+  <si>
+    <t>Workflow status for receipt set to 'Failed', and failure message captured in workflow result.</t>
+  </si>
+  <si>
+    <t>Pass – Verified via automated unit test test_genuine_receipt_tool_failure. Receipt status recorded as 'Failed' gracefully.</t>
+  </si>
+  <si>
+    <t>Short-Term Session Memory Storage &amp; Follow-Up Context</t>
+  </si>
+  <si>
+    <t>Complete an audit under a unique session_id, then submit a follow-up query using CoordinatorAgent.handle_follow_up().</t>
+  </si>
+  <si>
+    <t>SESSION_STORE retains expense details, audit results, and message history keyed by session_id.</t>
+  </si>
+  <si>
+    <t>Coordinator retrieves past expense context and previous audit result from SESSION_STORE and provides context-aware follow-up answer.</t>
+  </si>
+  <si>
+    <t>Pass – Verified via automated unit test test_short_term_memory (mocked LLM). Follow-up query successfully accessed session context. Note: Session memory is lost on server restart.</t>
+  </si>
+  <si>
+    <t>Gemini API Quota Exhaustion (429 Rate Limit) Graceful Handling</t>
+  </si>
+  <si>
+    <t>Simulate a 429 RESOURCE_EXHAUSTED exception during handle_follow_up() invocation.</t>
+  </si>
+  <si>
+    <t>Error handler detects 429/quota error, masks raw stack traces/keys, preserves SESSION_STORE data, and returns user-friendly fallback.</t>
+  </si>
+  <si>
+    <t>System returns friendly message: 'The AI service has temporarily reached its usage limit. Please try again later.' Raw API error, keys, and 429 status codes are suppressed. Session state remains intact.</t>
+  </si>
+  <si>
+    <t>Pass – Verified via automated unit test test_gemini_429_quota_exhaustion_in_chat (mocked 429 exception). Returned exact user-friendly fallback, session data preserved.</t>
+  </si>
+  <si>
+    <t>Missing Session Context Error Handling in Chat</t>
+  </si>
+  <si>
+    <t>Call CoordinatorAgent.handle_follow_up() with an invalid/unregistered session_id ('invalid_session').</t>
+  </si>
+  <si>
+    <t>System checks SESSION_STORE for active session context before invoking LLM.</t>
+  </si>
+  <si>
+    <t>System returns 'No active session context found. Please submit an expense first.' without sending request to LLM.</t>
+  </si>
+  <si>
+    <t>Pass – Verified via automated unit test test_missing_context. Correct error message returned instantly.</t>
+  </si>
+  <si>
+    <t>Empty LLM Response Handling in Analysis &amp; Decision Agents</t>
+  </si>
+  <si>
+    <t>Simulate empty text/content returned by Gemini LLM during Analysis and Decision Support agent steps.</t>
+  </si>
+  <si>
+    <t>Agent handles empty response object gracefully without returning None or crashing string operations.</t>
+  </si>
+  <si>
+    <t>Analysis Agent returns 'Analysis completed with no additional findings.' Decision Support Agent returns 'Decision support analysis completed with no summary available.'</t>
+  </si>
+  <si>
+    <t>Pass – Verified via automated unit test test_empty_model_responses. Both agents returned proper fallback text strings.</t>
+  </si>
+  <si>
+    <t>Web UI /api/chat Follow-Up Endpoint Integration</t>
+  </si>
+  <si>
+    <t>Send POST request to /api/chat with JSON body containing user follow-up message and session cookie.</t>
+  </si>
+  <si>
+    <t>Flask route extracts session ID, validates input message, calls Coordinator handle_follow_up(), and returns JSON response.</t>
+  </si>
+  <si>
+    <t>Returns HTTP 200 with JSON payload {'response': '...'}; returns HTTP 400 if message or session context missing.</t>
+  </si>
+  <si>
+    <t>Planned / Pending Manual UI Verification – Code logic verified via static analysis in web_app.py lines 323-340; live browser interaction requires manual verification.</t>
+  </si>
+  <si>
+    <t>Advisory Audit Guardrails Verification</t>
+  </si>
+  <si>
+    <t>Inspect generated reports from Decision Support Agent across various expense scenarios.</t>
+  </si>
+  <si>
+    <t>System prompts strictly enforce advisory tone ('potential risk', 'requires review', 'recommendation') and prevent definitive fraud accusations or binding financial approvals/rejections.</t>
+  </si>
+  <si>
+    <t>Report provides explainable advisory recommendations for human reviewers without issuing binding financial verdicts.</t>
+  </si>
+  <si>
+    <t>Pass – Verified via prompt design and agent system instructions in app/agents/decision_support_agent.py lines 10-12 and unit test suite.</t>
   </si>
 </sst>
 </file>
@@ -288,16 +483,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Calibri "/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Calibri "/>
     </font>
     <font>
@@ -311,6 +496,16 @@
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri "/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -327,7 +522,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -350,49 +545,38 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -708,356 +892,626 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="7" customWidth="1"/>
-    <col min="2" max="2" width="27.08984375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="30.6328125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="33" style="7" customWidth="1"/>
-    <col min="5" max="5" width="31.36328125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="27.08984375" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="7"/>
+    <col min="1" max="1" width="9.1796875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="27.08984375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="30.6328125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="33" style="4" customWidth="1"/>
+    <col min="5" max="5" width="31.36328125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="27.08984375" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="15.5">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="15.5">
+      <c r="A1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="4"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="64.5" customHeight="1">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="8"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" spans="1:7" ht="70.5" customHeight="1">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="6"/>
-    </row>
-    <row r="4" spans="1:7" ht="62.5">
-      <c r="A4" s="2">
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" ht="93">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="6"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="170.5">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" spans="1:7" ht="75">
-      <c r="A6" s="2">
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:7" ht="108.5">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="8"/>
-    </row>
-    <row r="7" spans="1:7" ht="62.5">
-      <c r="A7" s="2">
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" ht="108.5">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" ht="50">
-      <c r="A8" s="2">
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="1:7" ht="77.5">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:7" ht="87.5">
-      <c r="A9" s="2">
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:7" ht="139.5">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:7" ht="62.5">
-      <c r="A10" s="2">
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="1:7" ht="108.5">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:7" ht="50">
-      <c r="A11" s="2">
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" ht="77.5">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" ht="87.5">
-      <c r="A12" s="2">
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" ht="124">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:7" ht="87.5">
-      <c r="A13" s="2">
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" ht="139.5">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G13" s="6"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" ht="97.5" customHeight="1">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G14" s="6"/>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" ht="100.5" customHeight="1">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:7" ht="87.5">
-      <c r="A16" s="2">
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" ht="124">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:1" ht="15.5">
-      <c r="A17" s="1"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7" ht="108.5">
+      <c r="A17" s="8">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="9"/>
+    </row>
+    <row r="18" spans="1:7" ht="93">
+      <c r="A18" s="8">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="9"/>
+    </row>
+    <row r="19" spans="1:7" ht="93">
+      <c r="A19" s="8">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="9"/>
+    </row>
+    <row r="20" spans="1:7" ht="93">
+      <c r="A20" s="8">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="9"/>
+    </row>
+    <row r="21" spans="1:7" ht="108.5">
+      <c r="A21" s="8">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" s="9"/>
+    </row>
+    <row r="22" spans="1:7" ht="108.5">
+      <c r="A22" s="8">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G22" s="9"/>
+    </row>
+    <row r="23" spans="1:7" ht="93">
+      <c r="A23" s="8">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" s="9"/>
+    </row>
+    <row r="24" spans="1:7" ht="124">
+      <c r="A24" s="8">
+        <v>23</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="9"/>
+    </row>
+    <row r="25" spans="1:7" ht="108.5">
+      <c r="A25" s="8">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="G25" s="9"/>
+    </row>
+    <row r="26" spans="1:7" ht="77.5">
+      <c r="A26" s="8">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" s="9"/>
+    </row>
+    <row r="27" spans="1:7" ht="93">
+      <c r="A27" s="8">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G27" s="9"/>
+    </row>
+    <row r="28" spans="1:7" ht="93">
+      <c r="A28" s="8">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="G28" s="9"/>
+    </row>
+    <row r="29" spans="1:7" ht="108.5">
+      <c r="A29" s="8">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G29" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
